--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92538159044</v>
+        <v>46157.93111898986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111898986</v>
+        <v>46157.93366984625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93366984625</v>
+        <v>46157.93669394997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93669394997</v>
+        <v>46158.28193155136</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28193155136</v>
+        <v>46158.29715825808</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29715825808</v>
+        <v>46158.29788784236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29788784236</v>
+        <v>46158.33354644832</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354644832</v>
+        <v>46158.37209955273</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209955273</v>
+        <v>46158.37267062888</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
